--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1178,122 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128011544</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98479</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr 303, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>403169</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6780536</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98501</v>
+        <v>98594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98594</v>
+        <v>98608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1294,6 +1294,237 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128138485</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105726</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hemfjället Ö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>402943</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6780530</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128138396</v>
+      </c>
+      <c r="B8" t="n">
+        <v>88939</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>510</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hemfjället Ö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>402983</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6780548</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105726</v>
+        <v>105752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105752</v>
+        <v>105754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105754</v>
+        <v>105755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105755</v>
+        <v>105759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105759</v>
+        <v>105761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105761</v>
+        <v>105765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105765</v>
+        <v>105775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105775</v>
+        <v>105778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105778</v>
+        <v>105807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105807</v>
+        <v>105819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105819</v>
+        <v>105820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>128138485</v>
       </c>
       <c r="B7" t="n">
-        <v>105820</v>
+        <v>105825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>128138396</v>
       </c>
       <c r="B8" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60978352</v>
+        <v>128138396</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Josmyran, S om Lindvallen, Dlr</t>
+          <t>Hemfjället Ö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403151.6378382923</v>
+        <v>402983</v>
       </c>
       <c r="R2" t="n">
-        <v>6780534.080476257</v>
+        <v>6780548</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,87 +761,79 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granskogsbryn, fuktig, sluttande</t>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Henrik Liliedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Henrik Liliedahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60978354</v>
+        <v>86596043</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Josmyran, S om Lindvallen, Dlr</t>
+          <t>Sälenfjällen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403152.0602973034</v>
+        <v>403219</v>
       </c>
       <c r="R3" t="n">
-        <v>6780514.262138535</v>
+        <v>6780540</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,85 +876,61 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Granskogsbryn, fuktig, sluttande</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60978349</v>
+        <v>86596349</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Josmyran, S om Lindvallen, Dlr</t>
+          <t>Sälenfjällen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403171.765972186</v>
+        <v>403071</v>
       </c>
       <c r="R4" t="n">
-        <v>6780544.637802309</v>
+        <v>6780511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,58 +973,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Granskogsbryn, fuktig, sluttande</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86596349</v>
+        <v>86596040</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1108,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403071.1722482305</v>
+        <v>403219</v>
       </c>
       <c r="R5" t="n">
-        <v>6780511.174413028</v>
+        <v>6780540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,19 +1057,9 @@
           <t>2019-08-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,7 +1089,7 @@
         <v>128011544</v>
       </c>
       <c r="B6" t="n">
-        <v>98608</v>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,56 +1202,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128138485</v>
+        <v>60978358</v>
       </c>
       <c r="B7" t="n">
-        <v>105825</v>
+        <v>101897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>220075</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemfjället Ö, Dlr</t>
+          <t>Josmyran, S om Lindvallen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402943</v>
+        <v>403143</v>
       </c>
       <c r="R7" t="n">
-        <v>6780530</v>
+        <v>6780484</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,12 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2016-08-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2016-08-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,34 +1281,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Grannaturskog</t>
+          <t>Surdrog i sluttande granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henrik Liliedahl</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Liliedahl</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128138396</v>
+        <v>86596098</v>
       </c>
       <c r="B8" t="n">
-        <v>88992</v>
+        <v>101897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,44 +1315,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>220075</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hemfjället Ö, Dlr</t>
+          <t>Sälenfjällen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402983</v>
+        <v>403066</v>
       </c>
       <c r="R8" t="n">
-        <v>6780548</v>
+        <v>6780464</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,12 +1369,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,37 +1383,693 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128138485</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hemfjället Ö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>402943</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6780530</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Henrik Liliedahl</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Henrik Liliedahl</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>60978348</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Josmyran, S om Lindvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>403211</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6780545</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granskogsbryn, fuktig, sluttande</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>60978349</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Josmyran, S om Lindvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>403172</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6780545</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granskogsbryn, fuktig, sluttande</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>60978352</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Josmyran, S om Lindvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>403152</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6780534</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Granskogsbryn, fuktig, sluttande</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>60978354</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Josmyran, S om Lindvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>403152</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6780514</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Granskogsbryn, fuktig, sluttande</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>86596028</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sälenfjällen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>403064</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6780534</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36089-2024 artfynd.xlsx
+++ b/artfynd/A 36089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128138396</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86596043</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86596349</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86596040</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128011544</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978358</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86596098</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128138485</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978348</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978349</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978352</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978354</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,8 +2135,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86596028</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>